--- a/plc/s7-1x00/core/system/esc/EOperatingCycle-v1.0.xlsx
+++ b/plc/s7-1x00/core/system/esc/EOperatingCycle-v1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PlcFramework\code\plc\s7-1x00\core\system\esc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C01A4E-BC23-41B8-8EA8-F8D340129C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BAFED6A-F8FB-4A9C-936D-3A1D5DCAB48A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18570" yWindow="-16365" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Constants" sheetId="1" r:id="rId1"/>
@@ -94,7 +94,7 @@
     <t>EOperatingCycle</t>
   </si>
   <si>
-    <t>{"version":"v1.0","author":"cyanezf","family":"core/system/esc"}</t>
+    <t>{"version":"v1.0","author":"cyanezf","family":"core/system/esc","status": "current", "deprecatedBy": null, "dependencies"  : []}</t>
   </si>
 </sst>
 </file>
@@ -472,7 +472,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.75" bestFit="1" customWidth="1"/>
@@ -481,7 +481,7 @@
     <col min="5" max="5" width="45" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,7 +498,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -515,7 +515,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -532,7 +532,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -549,7 +549,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -566,7 +566,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -583,7 +583,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
